--- a/data/official_data/knowledge/university_info.xlsx
+++ b/data/official_data/knowledge/university_info.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="55">
   <si>
     <t>Intent</t>
   </si>
@@ -130,16 +130,82 @@
   </si>
   <si>
     <t>https://www.cusrinagar.edu.in/Home/AboutCUS</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Chancellor</t>
+  </si>
+  <si>
+    <t>Vice Chancellor</t>
+  </si>
+  <si>
+    <t>Registrar</t>
+  </si>
+  <si>
+    <t>Controller of Examinations</t>
+  </si>
+  <si>
+    <t>Manoj Sinha (Lieutenant Governor of Jammu and Kashmir)</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Mohammad Mobin</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Syed Wilayat Hussain Rizvi</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Khursheed Ahmad Mir</t>
+  </si>
+  <si>
+    <t>controller@cusrinagar.edu.in</t>
+  </si>
+  <si>
+    <t>registrar@cusrinagar.edu.in</t>
+  </si>
+  <si>
+    <t>drmmobin@hotmail.com</t>
+  </si>
+  <si>
+    <t>Pro Chancellor</t>
+  </si>
+  <si>
+    <t>Ms Sakina Masood Itoo</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>https://www.cusrinagar.edu.in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -162,16 +228,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -182,66 +255,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>1610</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6829425" y="0"/>
-          <a:ext cx="885825" cy="312048525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,12 +544,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.140625" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
@@ -577,11 +590,11 @@
       <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -597,8 +610,11 @@
       <c r="E3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -614,8 +630,11 @@
       <c r="E4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -631,8 +650,11 @@
       <c r="E5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -648,8 +670,11 @@
       <c r="E6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -665,6 +690,9 @@
       <c r="E7" t="s">
         <v>24</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -682,6 +710,9 @@
       <c r="E8" t="s">
         <v>24</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -699,6 +730,9 @@
       <c r="E9" t="s">
         <v>24</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -716,8 +750,11 @@
       <c r="E10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -733,8 +770,11 @@
       <c r="E11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -750,6 +790,9 @@
       <c r="E12" t="s">
         <v>24</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -767,9 +810,11 @@
       <c r="E13" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -785,6 +830,9 @@
       <c r="E14" t="s">
         <v>24</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -802,11 +850,153 @@
       <c r="E15" t="s">
         <v>24</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F20" r:id="rId1"/>
+    <hyperlink ref="F19" r:id="rId2" display="mailto:registrar@cusrinagar.edu.in?Subject=ClusterUniversity"/>
+    <hyperlink ref="D21" r:id="rId3"/>
+    <hyperlink ref="F17" r:id="rId4"/>
+    <hyperlink ref="F2" r:id="rId5"/>
+    <hyperlink ref="F3" r:id="rId6"/>
+    <hyperlink ref="F4" r:id="rId7"/>
+    <hyperlink ref="F5" r:id="rId8"/>
+    <hyperlink ref="F6" r:id="rId9"/>
+    <hyperlink ref="F7" r:id="rId10"/>
+    <hyperlink ref="F8" r:id="rId11"/>
+    <hyperlink ref="F9" r:id="rId12"/>
+    <hyperlink ref="F10" r:id="rId13"/>
+    <hyperlink ref="F11" r:id="rId14"/>
+    <hyperlink ref="F12" r:id="rId15"/>
+    <hyperlink ref="F13" r:id="rId16"/>
+    <hyperlink ref="F14" r:id="rId17"/>
+    <hyperlink ref="F15" r:id="rId18"/>
+    <hyperlink ref="F16" r:id="rId19"/>
+    <hyperlink ref="F21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
 

--- a/data/official_data/knowledge/university_info.xlsx
+++ b/data/official_data/knowledge/university_info.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="56">
   <si>
     <t>Intent</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>https://www.cusrinagar.edu.in</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -544,17 +547,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,8 +578,11 @@
       <c r="F1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -594,7 +602,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -614,7 +622,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -634,7 +642,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -654,7 +662,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -674,7 +682,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -694,7 +702,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -714,7 +722,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -734,7 +742,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -754,7 +762,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -774,7 +782,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -794,7 +802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -814,7 +822,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -834,7 +842,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -854,7 +862,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -874,7 +882,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -890,11 +898,11 @@
       <c r="E17" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -912,7 +920,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -928,11 +936,12 @@
       <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -948,11 +957,11 @@
       <c r="E20" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -974,26 +983,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F20" r:id="rId1"/>
-    <hyperlink ref="F19" r:id="rId2" display="mailto:registrar@cusrinagar.edu.in?Subject=ClusterUniversity"/>
-    <hyperlink ref="D21" r:id="rId3"/>
-    <hyperlink ref="F17" r:id="rId4"/>
-    <hyperlink ref="F2" r:id="rId5"/>
-    <hyperlink ref="F3" r:id="rId6"/>
-    <hyperlink ref="F4" r:id="rId7"/>
-    <hyperlink ref="F5" r:id="rId8"/>
-    <hyperlink ref="F6" r:id="rId9"/>
-    <hyperlink ref="F7" r:id="rId10"/>
-    <hyperlink ref="F8" r:id="rId11"/>
-    <hyperlink ref="F9" r:id="rId12"/>
-    <hyperlink ref="F10" r:id="rId13"/>
-    <hyperlink ref="F11" r:id="rId14"/>
-    <hyperlink ref="F12" r:id="rId15"/>
-    <hyperlink ref="F13" r:id="rId16"/>
-    <hyperlink ref="F14" r:id="rId17"/>
-    <hyperlink ref="F15" r:id="rId18"/>
-    <hyperlink ref="F16" r:id="rId19"/>
-    <hyperlink ref="F21" r:id="rId20"/>
+    <hyperlink ref="G20" r:id="rId1"/>
+    <hyperlink ref="D21" r:id="rId2"/>
+    <hyperlink ref="G17" r:id="rId3"/>
+    <hyperlink ref="F2" r:id="rId4"/>
+    <hyperlink ref="F3" r:id="rId5"/>
+    <hyperlink ref="F4" r:id="rId6"/>
+    <hyperlink ref="F5" r:id="rId7"/>
+    <hyperlink ref="F6" r:id="rId8"/>
+    <hyperlink ref="F7" r:id="rId9"/>
+    <hyperlink ref="F8" r:id="rId10"/>
+    <hyperlink ref="F9" r:id="rId11"/>
+    <hyperlink ref="F10" r:id="rId12"/>
+    <hyperlink ref="F11" r:id="rId13"/>
+    <hyperlink ref="F12" r:id="rId14"/>
+    <hyperlink ref="F13" r:id="rId15"/>
+    <hyperlink ref="F14" r:id="rId16"/>
+    <hyperlink ref="F15" r:id="rId17"/>
+    <hyperlink ref="F16" r:id="rId18"/>
+    <hyperlink ref="F21" r:id="rId19"/>
+    <hyperlink ref="G19" r:id="rId20" display="mailto:registrar@cusrinagar.edu.in?Subject=ClusterUniversity"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>

--- a/data/official_data/knowledge/university_info.xlsx
+++ b/data/official_data/knowledge/university_info.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
   <si>
     <t>Intent</t>
   </si>
@@ -184,6 +184,18 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Cluster University Srinagar (CUS) is a state university established in 2016 under the Srinagar and Jammu Cluster Universities Act, 2016. It was established through a cluster model involving five constituent colleges in Srinagar and focuses on quality higher education, teaching, research, innovation, skill development and holistic development of students.</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Gogji Bagh, Srinagar – 190008, Jammu and Kashmir</t>
   </si>
 </sst>
 </file>
@@ -235,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -245,6 +257,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -547,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -978,6 +999,46 @@
         <v>24</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1003,9 +1064,11 @@
     <hyperlink ref="F16" r:id="rId18"/>
     <hyperlink ref="F21" r:id="rId19"/>
     <hyperlink ref="G19" r:id="rId20" display="mailto:registrar@cusrinagar.edu.in?Subject=ClusterUniversity"/>
+    <hyperlink ref="F22" r:id="rId21"/>
+    <hyperlink ref="F23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
 </worksheet>
 </file>
 

--- a/data/official_data/knowledge/university_info.xlsx
+++ b/data/official_data/knowledge/university_info.xlsx
@@ -1026,13 +1026,13 @@
       <c r="A23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E23" s="5" t="s">
